--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121241364</v>
+        <v>121238089</v>
       </c>
       <c r="B8" t="n">
-        <v>90687</v>
+        <v>79679</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498786</v>
+        <v>498515</v>
       </c>
       <c r="R8" t="n">
-        <v>7040556</v>
+        <v>7040933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238089</v>
+        <v>121241364</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>90687</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498515</v>
+        <v>498786</v>
       </c>
       <c r="R9" t="n">
-        <v>7040933</v>
+        <v>7040556</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237900</v>
+        <v>121241330</v>
       </c>
       <c r="B6" t="n">
-        <v>90687</v>
+        <v>98417</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,30 +1112,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498424</v>
+        <v>498719</v>
       </c>
       <c r="R6" t="n">
-        <v>7040549</v>
+        <v>7040416</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121241330</v>
+        <v>121237900</v>
       </c>
       <c r="B7" t="n">
-        <v>98407</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,31 +1219,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498719</v>
+        <v>498424</v>
       </c>
       <c r="R7" t="n">
-        <v>7040416</v>
+        <v>7040549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1316,7 @@
         <v>121238089</v>
       </c>
       <c r="B8" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241364</v>
+        <v>121241352</v>
       </c>
       <c r="B9" t="n">
-        <v>90687</v>
+        <v>79682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498786</v>
+        <v>498728</v>
       </c>
       <c r="R9" t="n">
-        <v>7040556</v>
+        <v>7040488</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121241374</v>
+        <v>121238093</v>
       </c>
       <c r="B10" t="n">
-        <v>90705</v>
+        <v>90697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498833</v>
+        <v>498549</v>
       </c>
       <c r="R10" t="n">
-        <v>7040500</v>
+        <v>7040889</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121238093</v>
+        <v>121238097</v>
       </c>
       <c r="B11" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498549</v>
+        <v>498717</v>
       </c>
       <c r="R11" t="n">
-        <v>7040889</v>
+        <v>7040823</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241352</v>
+        <v>121241364</v>
       </c>
       <c r="B12" t="n">
-        <v>79679</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498728</v>
+        <v>498786</v>
       </c>
       <c r="R12" t="n">
-        <v>7040488</v>
+        <v>7040556</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121238097</v>
+        <v>121241374</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>90715</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498717</v>
+        <v>498833</v>
       </c>
       <c r="R13" t="n">
-        <v>7040823</v>
+        <v>7040500</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121241330</v>
+        <v>121241364</v>
       </c>
       <c r="B6" t="n">
-        <v>98417</v>
+        <v>90697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,31 +1112,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498719</v>
+        <v>498786</v>
       </c>
       <c r="R6" t="n">
-        <v>7040416</v>
+        <v>7040556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121237900</v>
+        <v>121237902</v>
       </c>
       <c r="B7" t="n">
         <v>90697</v>
@@ -1313,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238089</v>
+        <v>121238093</v>
       </c>
       <c r="B8" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498515</v>
+        <v>498549</v>
       </c>
       <c r="R8" t="n">
-        <v>7040933</v>
+        <v>7040889</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241352</v>
+        <v>121238097</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498728</v>
+        <v>498717</v>
       </c>
       <c r="R9" t="n">
-        <v>7040488</v>
+        <v>7040823</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121238093</v>
+        <v>121241352</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498549</v>
+        <v>498728</v>
       </c>
       <c r="R10" t="n">
-        <v>7040889</v>
+        <v>7040488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121238097</v>
+        <v>121241374</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>90715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498717</v>
+        <v>498833</v>
       </c>
       <c r="R11" t="n">
-        <v>7040823</v>
+        <v>7040500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241364</v>
+        <v>121241330</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
+        <v>98417</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,30 +1748,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498786</v>
+        <v>498719</v>
       </c>
       <c r="R12" t="n">
-        <v>7040556</v>
+        <v>7040416</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121241374</v>
+        <v>121238089</v>
       </c>
       <c r="B13" t="n">
-        <v>90715</v>
+        <v>79682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498833</v>
+        <v>498515</v>
       </c>
       <c r="R13" t="n">
-        <v>7040500</v>
+        <v>7040933</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121241364</v>
+        <v>121238089</v>
       </c>
       <c r="B6" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498786</v>
+        <v>498515</v>
       </c>
       <c r="R6" t="n">
-        <v>7040556</v>
+        <v>7040933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121237902</v>
+        <v>121238093</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498424</v>
+        <v>498549</v>
       </c>
       <c r="R7" t="n">
-        <v>7040549</v>
+        <v>7040889</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238093</v>
+        <v>121237900</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498549</v>
+        <v>498424</v>
       </c>
       <c r="R8" t="n">
-        <v>7040889</v>
+        <v>7040549</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238097</v>
+        <v>121241364</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498717</v>
+        <v>498786</v>
       </c>
       <c r="R9" t="n">
-        <v>7040823</v>
+        <v>7040556</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121241352</v>
+        <v>121238097</v>
       </c>
       <c r="B10" t="n">
-        <v>79682</v>
+        <v>90709</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498728</v>
+        <v>498717</v>
       </c>
       <c r="R10" t="n">
-        <v>7040488</v>
+        <v>7040823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241374</v>
+        <v>121241352</v>
       </c>
       <c r="B11" t="n">
-        <v>90715</v>
+        <v>79685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498833</v>
+        <v>498728</v>
       </c>
       <c r="R11" t="n">
-        <v>7040500</v>
+        <v>7040488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241330</v>
+        <v>121241374</v>
       </c>
       <c r="B12" t="n">
-        <v>98417</v>
+        <v>90727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,31 +1748,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498719</v>
+        <v>498833</v>
       </c>
       <c r="R12" t="n">
-        <v>7040416</v>
+        <v>7040500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121238089</v>
+        <v>121241330</v>
       </c>
       <c r="B13" t="n">
-        <v>79682</v>
+        <v>98430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,30 +1854,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498515</v>
+        <v>498719</v>
       </c>
       <c r="R13" t="n">
-        <v>7040933</v>
+        <v>7040416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238089</v>
+        <v>121237902</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498515</v>
+        <v>498424</v>
       </c>
       <c r="R6" t="n">
-        <v>7040933</v>
+        <v>7040549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1209,7 @@
         <v>121238093</v>
       </c>
       <c r="B7" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237900</v>
+        <v>121241352</v>
       </c>
       <c r="B8" t="n">
-        <v>90709</v>
+        <v>79685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498424</v>
+        <v>498728</v>
       </c>
       <c r="R8" t="n">
-        <v>7040549</v>
+        <v>7040488</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241364</v>
+        <v>121241374</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498786</v>
+        <v>498833</v>
       </c>
       <c r="R9" t="n">
-        <v>7040556</v>
+        <v>7040500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121238097</v>
+        <v>121241330</v>
       </c>
       <c r="B10" t="n">
-        <v>90709</v>
+        <v>98431</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,30 +1536,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1567,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498717</v>
+        <v>498719</v>
       </c>
       <c r="R10" t="n">
-        <v>7040823</v>
+        <v>7040416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241352</v>
+        <v>121238097</v>
       </c>
       <c r="B11" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498728</v>
+        <v>498717</v>
       </c>
       <c r="R11" t="n">
-        <v>7040488</v>
+        <v>7040823</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241374</v>
+        <v>121238089</v>
       </c>
       <c r="B12" t="n">
-        <v>90727</v>
+        <v>79685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498833</v>
+        <v>498515</v>
       </c>
       <c r="R12" t="n">
-        <v>7040500</v>
+        <v>7040933</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121241330</v>
+        <v>121241364</v>
       </c>
       <c r="B13" t="n">
-        <v>98430</v>
+        <v>90710</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,31 +1855,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498719</v>
+        <v>498786</v>
       </c>
       <c r="R13" t="n">
-        <v>7040416</v>
+        <v>7040556</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237902</v>
+        <v>121241374</v>
       </c>
       <c r="B6" t="n">
-        <v>90710</v>
+        <v>90731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498424</v>
+        <v>498833</v>
       </c>
       <c r="R6" t="n">
-        <v>7040549</v>
+        <v>7040500</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238093</v>
+        <v>121238097</v>
       </c>
       <c r="B7" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498549</v>
+        <v>498717</v>
       </c>
       <c r="R7" t="n">
-        <v>7040889</v>
+        <v>7040823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121241352</v>
+        <v>121238093</v>
       </c>
       <c r="B8" t="n">
-        <v>79685</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498728</v>
+        <v>498549</v>
       </c>
       <c r="R8" t="n">
-        <v>7040488</v>
+        <v>7040889</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241374</v>
+        <v>121241352</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>79688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498833</v>
+        <v>498728</v>
       </c>
       <c r="R9" t="n">
-        <v>7040500</v>
+        <v>7040488</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121241330</v>
+        <v>121241364</v>
       </c>
       <c r="B10" t="n">
-        <v>98431</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,31 +1536,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498719</v>
+        <v>498786</v>
       </c>
       <c r="R10" t="n">
-        <v>7040416</v>
+        <v>7040556</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121238097</v>
+        <v>121237900</v>
       </c>
       <c r="B11" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498717</v>
+        <v>498424</v>
       </c>
       <c r="R11" t="n">
-        <v>7040823</v>
+        <v>7040549</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121238089</v>
+        <v>121241330</v>
       </c>
       <c r="B12" t="n">
-        <v>79685</v>
+        <v>98434</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,30 +1748,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498515</v>
+        <v>498719</v>
       </c>
       <c r="R12" t="n">
-        <v>7040933</v>
+        <v>7040416</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121241364</v>
+        <v>121238089</v>
       </c>
       <c r="B13" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498786</v>
+        <v>498515</v>
       </c>
       <c r="R13" t="n">
-        <v>7040556</v>
+        <v>7040933</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121241374</v>
+        <v>121237900</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
+        <v>90713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498833</v>
+        <v>498424</v>
       </c>
       <c r="R6" t="n">
-        <v>7040500</v>
+        <v>7040549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238097</v>
+        <v>121238093</v>
       </c>
       <c r="B7" t="n">
         <v>90713</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498717</v>
+        <v>498549</v>
       </c>
       <c r="R7" t="n">
-        <v>7040823</v>
+        <v>7040889</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238093</v>
+        <v>121241374</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>90731</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498549</v>
+        <v>498833</v>
       </c>
       <c r="R8" t="n">
-        <v>7040889</v>
+        <v>7040500</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241352</v>
+        <v>121238097</v>
       </c>
       <c r="B9" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498728</v>
+        <v>498717</v>
       </c>
       <c r="R9" t="n">
-        <v>7040488</v>
+        <v>7040823</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121241364</v>
+        <v>121238089</v>
       </c>
       <c r="B10" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498786</v>
+        <v>498515</v>
       </c>
       <c r="R10" t="n">
-        <v>7040556</v>
+        <v>7040933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121237900</v>
+        <v>121241364</v>
       </c>
       <c r="B11" t="n">
         <v>90713</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498424</v>
+        <v>498786</v>
       </c>
       <c r="R11" t="n">
-        <v>7040549</v>
+        <v>7040556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121238089</v>
+        <v>121241352</v>
       </c>
       <c r="B13" t="n">
         <v>79688</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498515</v>
+        <v>498728</v>
       </c>
       <c r="R13" t="n">
-        <v>7040933</v>
+        <v>7040488</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121241374</v>
+        <v>121238089</v>
       </c>
       <c r="B8" t="n">
-        <v>90731</v>
+        <v>79688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498833</v>
+        <v>498515</v>
       </c>
       <c r="R8" t="n">
-        <v>7040500</v>
+        <v>7040933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238097</v>
+        <v>121241374</v>
       </c>
       <c r="B9" t="n">
-        <v>90713</v>
+        <v>90731</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498717</v>
+        <v>498833</v>
       </c>
       <c r="R9" t="n">
-        <v>7040823</v>
+        <v>7040500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121238089</v>
+        <v>121238097</v>
       </c>
       <c r="B10" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498515</v>
+        <v>498717</v>
       </c>
       <c r="R10" t="n">
-        <v>7040933</v>
+        <v>7040823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237900</v>
+        <v>121241374</v>
       </c>
       <c r="B6" t="n">
-        <v>90713</v>
+        <v>90737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498424</v>
+        <v>498833</v>
       </c>
       <c r="R6" t="n">
-        <v>7040549</v>
+        <v>7040500</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238093</v>
+        <v>121241330</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
+        <v>98440</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,30 +1218,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498549</v>
+        <v>498719</v>
       </c>
       <c r="R7" t="n">
-        <v>7040889</v>
+        <v>7040416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238089</v>
+        <v>121237900</v>
       </c>
       <c r="B8" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498515</v>
+        <v>498424</v>
       </c>
       <c r="R8" t="n">
-        <v>7040933</v>
+        <v>7040549</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241374</v>
+        <v>121238089</v>
       </c>
       <c r="B9" t="n">
-        <v>90731</v>
+        <v>79689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498833</v>
+        <v>498515</v>
       </c>
       <c r="R9" t="n">
-        <v>7040500</v>
+        <v>7040933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121238097</v>
+        <v>121238093</v>
       </c>
       <c r="B10" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498717</v>
+        <v>498549</v>
       </c>
       <c r="R10" t="n">
-        <v>7040823</v>
+        <v>7040889</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241364</v>
+        <v>121241352</v>
       </c>
       <c r="B11" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498786</v>
+        <v>498728</v>
       </c>
       <c r="R11" t="n">
-        <v>7040556</v>
+        <v>7040488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241330</v>
+        <v>121238097</v>
       </c>
       <c r="B12" t="n">
-        <v>98434</v>
+        <v>90719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,31 +1749,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498719</v>
+        <v>498717</v>
       </c>
       <c r="R12" t="n">
-        <v>7040416</v>
+        <v>7040823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121241352</v>
+        <v>121241364</v>
       </c>
       <c r="B13" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498728</v>
+        <v>498786</v>
       </c>
       <c r="R13" t="n">
-        <v>7040488</v>
+        <v>7040556</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121241374</v>
+        <v>121238093</v>
       </c>
       <c r="B6" t="n">
-        <v>90737</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498833</v>
+        <v>498549</v>
       </c>
       <c r="R6" t="n">
-        <v>7040500</v>
+        <v>7040889</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121241330</v>
+        <v>121238097</v>
       </c>
       <c r="B7" t="n">
-        <v>98440</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,31 +1218,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1250,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498719</v>
+        <v>498717</v>
       </c>
       <c r="R7" t="n">
-        <v>7040416</v>
+        <v>7040823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237900</v>
+        <v>121241330</v>
       </c>
       <c r="B8" t="n">
-        <v>90719</v>
+        <v>98441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,30 +1324,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498424</v>
+        <v>498719</v>
       </c>
       <c r="R8" t="n">
-        <v>7040549</v>
+        <v>7040416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>121238089</v>
       </c>
       <c r="B9" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121238093</v>
+        <v>121237900</v>
       </c>
       <c r="B10" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498549</v>
+        <v>498424</v>
       </c>
       <c r="R10" t="n">
-        <v>7040889</v>
+        <v>7040549</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241352</v>
+        <v>121241374</v>
       </c>
       <c r="B11" t="n">
-        <v>79689</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498728</v>
+        <v>498833</v>
       </c>
       <c r="R11" t="n">
-        <v>7040488</v>
+        <v>7040500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121238097</v>
+        <v>121241364</v>
       </c>
       <c r="B12" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498717</v>
+        <v>498786</v>
       </c>
       <c r="R12" t="n">
-        <v>7040823</v>
+        <v>7040556</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121241364</v>
+        <v>121241352</v>
       </c>
       <c r="B13" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498786</v>
+        <v>498728</v>
       </c>
       <c r="R13" t="n">
-        <v>7040556</v>
+        <v>7040488</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238093</v>
+        <v>121241352</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498549</v>
+        <v>498728</v>
       </c>
       <c r="R6" t="n">
-        <v>7040889</v>
+        <v>7040488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121241330</v>
+        <v>121237900</v>
       </c>
       <c r="B8" t="n">
-        <v>98441</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,31 +1324,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1356,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498719</v>
+        <v>498424</v>
       </c>
       <c r="R8" t="n">
-        <v>7040416</v>
+        <v>7040549</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238089</v>
+        <v>121238093</v>
       </c>
       <c r="B9" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498515</v>
+        <v>498549</v>
       </c>
       <c r="R9" t="n">
-        <v>7040933</v>
+        <v>7040889</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121237900</v>
+        <v>121241330</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
+        <v>98441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,30 +1536,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498424</v>
+        <v>498719</v>
       </c>
       <c r="R10" t="n">
-        <v>7040549</v>
+        <v>7040416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241374</v>
+        <v>121241364</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498833</v>
+        <v>498786</v>
       </c>
       <c r="R11" t="n">
-        <v>7040500</v>
+        <v>7040556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241364</v>
+        <v>121241374</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498786</v>
+        <v>498833</v>
       </c>
       <c r="R12" t="n">
-        <v>7040556</v>
+        <v>7040500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121241352</v>
+        <v>121238089</v>
       </c>
       <c r="B13" t="n">
         <v>79690</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498728</v>
+        <v>498515</v>
       </c>
       <c r="R13" t="n">
-        <v>7040488</v>
+        <v>7040933</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121241352</v>
+        <v>121237902</v>
       </c>
       <c r="B6" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498728</v>
+        <v>498424</v>
       </c>
       <c r="R6" t="n">
-        <v>7040488</v>
+        <v>7040549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237900</v>
+        <v>121241364</v>
       </c>
       <c r="B8" t="n">
         <v>90720</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498424</v>
+        <v>498786</v>
       </c>
       <c r="R8" t="n">
-        <v>7040549</v>
+        <v>7040556</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238093</v>
+        <v>121241374</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498549</v>
+        <v>498833</v>
       </c>
       <c r="R9" t="n">
-        <v>7040889</v>
+        <v>7040500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121241330</v>
+        <v>121238089</v>
       </c>
       <c r="B10" t="n">
-        <v>98441</v>
+        <v>79690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,31 +1536,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498719</v>
+        <v>498515</v>
       </c>
       <c r="R10" t="n">
-        <v>7040416</v>
+        <v>7040933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241364</v>
+        <v>121241330</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>98441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,30 +1642,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498786</v>
+        <v>498719</v>
       </c>
       <c r="R11" t="n">
-        <v>7040556</v>
+        <v>7040416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241374</v>
+        <v>121241352</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498833</v>
+        <v>498728</v>
       </c>
       <c r="R12" t="n">
-        <v>7040500</v>
+        <v>7040488</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121238089</v>
+        <v>121238093</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498515</v>
+        <v>498549</v>
       </c>
       <c r="R13" t="n">
-        <v>7040933</v>
+        <v>7040889</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -1100,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237902</v>
+        <v>121238097</v>
       </c>
       <c r="B6" t="n">
         <v>90720</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498424</v>
+        <v>498717</v>
       </c>
       <c r="R6" t="n">
-        <v>7040549</v>
+        <v>7040823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238097</v>
+        <v>121241330</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>98441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,30 +1218,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498717</v>
+        <v>498719</v>
       </c>
       <c r="R7" t="n">
-        <v>7040823</v>
+        <v>7040416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121241364</v>
+        <v>121238089</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498786</v>
+        <v>498515</v>
       </c>
       <c r="R8" t="n">
-        <v>7040556</v>
+        <v>7040933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241374</v>
+        <v>121237902</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498833</v>
+        <v>498424</v>
       </c>
       <c r="R9" t="n">
-        <v>7040500</v>
+        <v>7040549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121238089</v>
+        <v>121241352</v>
       </c>
       <c r="B10" t="n">
         <v>79690</v>
@@ -1567,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498515</v>
+        <v>498728</v>
       </c>
       <c r="R10" t="n">
-        <v>7040933</v>
+        <v>7040488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241330</v>
+        <v>121241374</v>
       </c>
       <c r="B11" t="n">
-        <v>98441</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,31 +1643,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498719</v>
+        <v>498833</v>
       </c>
       <c r="R11" t="n">
-        <v>7040416</v>
+        <v>7040500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241352</v>
+        <v>121241364</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498728</v>
+        <v>498786</v>
       </c>
       <c r="R12" t="n">
-        <v>7040488</v>
+        <v>7040556</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119501367</v>
+        <v>119501372</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498535</v>
+        <v>498564</v>
       </c>
       <c r="R2" t="n">
-        <v>7040935</v>
+        <v>7040869</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,54 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119501441</v>
+        <v>121237900</v>
       </c>
       <c r="B3" t="n">
-        <v>98242</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rismyrvägen, Jmt</t>
+          <t>Lassgård, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498733</v>
+        <v>498424</v>
       </c>
       <c r="R3" t="n">
-        <v>7040424</v>
+        <v>7040549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119501372</v>
+        <v>121238093</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rismyrvägen, Jmt</t>
+          <t>Lassgård, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498564</v>
+        <v>498549</v>
       </c>
       <c r="R4" t="n">
-        <v>7040869</v>
+        <v>7040889</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119501435</v>
+        <v>121238095</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,38 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rismyrvägen, Jmt</t>
+          <t>Lassgård, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498786</v>
+        <v>498579</v>
       </c>
       <c r="R5" t="n">
-        <v>7040745</v>
+        <v>7040798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,6 +1060,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,12 +1082,7 @@
         <v>121238097</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,43 +1180,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121241330</v>
+        <v>121241364</v>
       </c>
       <c r="B7" t="n">
-        <v>98441</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1250,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498719</v>
+        <v>498786</v>
       </c>
       <c r="R7" t="n">
-        <v>7040416</v>
+        <v>7040556</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238089</v>
+        <v>131889861</v>
       </c>
       <c r="B8" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,14 +1315,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lassgård, Jmt</t>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498515</v>
+        <v>498269</v>
       </c>
       <c r="R8" t="n">
-        <v>7040933</v>
+        <v>7040359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,12 +1349,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,30 +1372,55 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121237902</v>
+        <v>121238089</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498424</v>
+        <v>498515</v>
       </c>
       <c r="R9" t="n">
-        <v>7040549</v>
+        <v>7040933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,12 +1521,7 @@
         <v>121241352</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,15 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241374</v>
+        <v>119501435</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,37 +1630,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lassgård, Jmt</t>
+          <t>Rismyrvägen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498833</v>
+        <v>498786</v>
       </c>
       <c r="R11" t="n">
-        <v>7040500</v>
+        <v>7040745</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,12 +1688,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,7 +1702,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1737,53 +1720,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241364</v>
+        <v>119501345</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lassgård, Jmt</t>
+          <t>Rismyrvägen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498786</v>
+        <v>498400</v>
       </c>
       <c r="R12" t="n">
-        <v>7040556</v>
+        <v>7040905</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,12 +1789,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,53 +1822,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121238093</v>
+        <v>119501441</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lassgård, Jmt</t>
+          <t>Rismyrvägen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498549</v>
+        <v>498733</v>
       </c>
       <c r="R13" t="n">
-        <v>7040889</v>
+        <v>7040424</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,12 +1891,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1946,6 +1921,108 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121241330</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lassgård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>498719</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7040416</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54731-2024 artfynd.xlsx
+++ b/artfynd/A 54731-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119501372</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121237900</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238093</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238095</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238097</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241364</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131889861</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238089</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241352</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119501435</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119501345</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1921,6 +1981,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119501441</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,8 +2088,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>